--- a/Forecast/Тройники.xlsx
+++ b/Forecast/Тройники.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,34 +428,34 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Квартал</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Номенклатура.Бренд</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Номенклатура.Артикул </t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Номенклатура.Оригинальный номер</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Номенклатура.Артикул </t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>Номенклатура.Оригинальный номер расширенный</t>
@@ -464,69 +468,75 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Машина.Двигатель</t>
+          <t>Машина.Бренд</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Машина.Бренд</t>
+          <t>Машина.Модель техники</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Машина.Модель техники</t>
+          <t>Машина.Серия техники</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Машина.Серия техники</t>
+          <t>Лот.CRM год выпуска</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Серийный номер</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>Лот.CRM наработка</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Документ.Склад</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Количество</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Тип подъемника</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Тип двигателя</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>13.05.2025 9:13:46</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A2" s="1" t="n">
+        <v>45790.38456018519</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -545,67 +555,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
+          <t>BART024I00174</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2310</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>15.05.2025 9:15:37</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A3" s="1" t="n">
+        <v>45792.38584490741</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -624,67 +644,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>BART025B00047</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>1915</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>15.05.2025 9:26:58</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A4" s="1" t="n">
+        <v>45792.39372685185</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -703,67 +733,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA36RT</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA36RT</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BA36RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>BART024K00334</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>15.05.2025 9:28:40</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A5" s="1" t="n">
+        <v>45792.3949074074</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -782,67 +822,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>BART025C00064</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>21.05.2025 10:41:52</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A6" s="1" t="n">
+        <v>45798.44574074074</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -861,67 +911,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>BART024I00173</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>22.05.2025 13:30:18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A7" s="1" t="n">
+        <v>45799.56270833333</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -940,67 +1000,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
+          <t>BART025B00043</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>1443</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22.05.2025 15:23:29</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A8" s="1" t="n">
+        <v>45799.64130787037</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1019,67 +1089,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>BART024K00321</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>1926</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>23.05.2025 13:01:07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A9" s="1" t="n">
+        <v>45800.54244212963</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1098,67 +1178,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>BART025C00116</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2978</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>26.05.2025 11:10:44</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A10" s="1" t="n">
+        <v>45803.46578703704</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1177,67 +1267,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>BART024K00323</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>26.05.2025 11:19:07</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A11" s="1" t="n">
+        <v>45803.4716087963</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1256,67 +1356,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>BART024K00321</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>1926</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>26.05.2025 11:39:26</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A12" s="1" t="n">
+        <v>45803.48571759259</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1335,67 +1445,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>BART025C00091</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>1095</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>26.05.2025 11:49:34</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A13" s="1" t="n">
+        <v>45803.49275462963</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1414,67 +1534,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>BART025C00121</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>26.05.2025 11:53:05</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A14" s="1" t="n">
+        <v>45803.49519675926</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1493,67 +1623,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>BART025C00118</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>3090</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>28.05.2025 9:01:16</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A15" s="1" t="n">
+        <v>45805.37587962963</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1572,67 +1712,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>BART025C00117</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>2709</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>28.05.2025 9:10:57</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A16" s="1" t="n">
+        <v>45805.38260416667</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1651,67 +1801,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>BART025C00122</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>2497</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>28.05.2025 9:13:27</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A17" s="1" t="n">
+        <v>45805.38434027778</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1730,67 +1890,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>BART025C00120</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>2560</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>29.05.2025 11:38:47</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A18" s="1" t="n">
+        <v>45806.4852662037</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1809,67 +1979,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>BART025C00119</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>30.05.2025 12:50:17</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A19" s="1" t="n">
+        <v>45807.53491898148</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1888,67 +2068,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>BART025C00158</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>2332</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>02.06.2025 11:38:40</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A20" s="1" t="n">
+        <v>45810.48518518519</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1967,67 +2157,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>BART025C00115</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>2987</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>02.06.2025 12:01:12</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A21" s="1" t="n">
+        <v>45810.50083333333</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2046,67 +2246,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>BART025C00110</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>2060</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03.06.2025 12:49:07</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A22" s="1" t="n">
+        <v>45811.5341087963</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2125,67 +2335,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t>BART025C00111</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>2250</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>05.06.2025 9:45:41</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A23" s="1" t="n">
+        <v>45813.40672453704</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2204,67 +2424,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
+          <t>BART025C00090</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>18.06.2025 11:30:54</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A24" s="1" t="n">
+        <v>45826.47979166666</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2283,67 +2513,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>BART025C00113</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>739</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>19.06.2025 13:35:13</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A25" s="1" t="n">
+        <v>45827.56612268519</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2362,67 +2602,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t>BART025C00112</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>1350</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20.06.2025 11:25:32</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A26" s="1" t="n">
+        <v>45828.47606481481</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2441,67 +2691,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA36RT</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA36RT</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BA36RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>BART025D00172</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>1105</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20.06.2025 13:43:26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A27" s="1" t="n">
+        <v>45828.5718287037</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2520,67 +2780,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA36RT</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA36RT</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BA36RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t>BART025D00161</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>1083</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>23.06.2025 16:29:38</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A28" s="1" t="n">
+        <v>45831.68724537037</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2599,67 +2869,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>BART025D00217</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>1199</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>01.08.2025 10:16:35</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A29" s="1" t="n">
+        <v>45870.42818287037</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2678,63 +2958,73 @@
           <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>BART024I00178</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20.08.2025 10:24:07</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A30" s="1" t="n">
+        <v>45889.43341435185</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2753,63 +3043,73 @@
           <t>Подъемник коленчатый дизельный Dingli BA44RT</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA44RT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BA44RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>BART024K00306</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t xml:space="preserve"> Усть-Луга. Склад Запчастей для Сервиса</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>18.09.2025 15:03:59</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A31" s="1" t="n">
+        <v>45918.6277662037</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2828,67 +3128,77 @@
           <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>BART024D00051</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>26.12.2025 14:08:13</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="A32" s="1" t="n">
+        <v>46017.58903935185</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Тройник Т- обр.00001240A</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Dingli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2907,36 +3217,50 @@
           <t>Подъемник коленчатый дизельный Dingli BA41RT</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Dingli</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Dingli</t>
+          <t>BA41RT</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BA41RT</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>BART024I00175</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>ПТО СК запчасти для арендного парка</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>коленчатый</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Дизельный</t>
         </is>
       </c>
     </row>
